--- a/diseases/d167/2005-2009.xlsx
+++ b/diseases/d167/2005-2009.xlsx
@@ -1011,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8871,7 +8871,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN47" t="b">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN49" t="b">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN51" t="b">
@@ -10836,7 +10836,7 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN53" t="b">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN55" t="b">
@@ -11622,7 +11622,7 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN57" t="b">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN61" t="b">
@@ -19875,7 +19875,7 @@
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -20268,7 +20268,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20661,7 +20661,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -21054,7 +21054,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -21447,7 +21447,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -21840,7 +21840,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -22233,7 +22233,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="AM113" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN113" t="b">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN115" t="b">
@@ -23412,7 +23412,7 @@
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -23805,7 +23805,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -24198,7 +24198,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -32058,7 +32058,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -32451,7 +32451,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -33237,7 +33237,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -33630,7 +33630,7 @@
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -34023,7 +34023,7 @@
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34416,7 +34416,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -34809,7 +34809,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35202,7 +35202,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -35595,7 +35595,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -35988,7 +35988,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -36381,7 +36381,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -45420,7 +45420,7 @@
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -45813,7 +45813,7 @@
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -46206,7 +46206,7 @@
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -46599,7 +46599,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -46992,7 +46992,7 @@
       </c>
       <c r="AM237" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN237" t="b">
@@ -47385,7 +47385,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -47778,7 +47778,7 @@
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -48171,7 +48171,7 @@
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -48564,7 +48564,7 @@
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -48957,7 +48957,7 @@
       </c>
       <c r="AM247" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN247" t="b">
@@ -49350,7 +49350,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -49743,7 +49743,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -59961,7 +59961,7 @@
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -60354,7 +60354,7 @@
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -60747,7 +60747,7 @@
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -61140,7 +61140,7 @@
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -61533,7 +61533,7 @@
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -61926,7 +61926,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -62319,7 +62319,7 @@
       </c>
       <c r="AM315" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN315" t="b">
@@ -62712,7 +62712,7 @@
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN317" t="b">
@@ -63105,7 +63105,7 @@
       </c>
       <c r="AM319" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN319" t="b">
@@ -63498,7 +63498,7 @@
       </c>
       <c r="AM321" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN321" t="b">
@@ -63891,7 +63891,7 @@
       </c>
       <c r="AM323" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN323" t="b">

--- a/diseases/d167/2005-2009.xlsx
+++ b/diseases/d167/2005-2009.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -8075,7 +8075,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
@@ -9647,7 +9647,7 @@
       </c>
       <c r="AJ47" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK47" t="inlineStr">
@@ -10040,7 +10040,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -10433,7 +10433,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12005,7 +12005,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12398,7 +12398,7 @@
       </c>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -19865,7 +19865,7 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -20258,7 +20258,7 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -21437,7 +21437,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -21830,7 +21830,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -22223,7 +22223,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -22616,7 +22616,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -23009,7 +23009,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -23402,7 +23402,7 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -23795,7 +23795,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -24188,7 +24188,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -32048,7 +32048,7 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
@@ -32441,7 +32441,7 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
@@ -32834,7 +32834,7 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
@@ -33227,7 +33227,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -33620,7 +33620,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -34013,7 +34013,7 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
@@ -34406,7 +34406,7 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
@@ -34799,7 +34799,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -35192,7 +35192,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -35585,7 +35585,7 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
@@ -35978,7 +35978,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -36371,7 +36371,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -45410,7 +45410,7 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
@@ -45803,7 +45803,7 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
@@ -46196,7 +46196,7 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
@@ -46589,7 +46589,7 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
@@ -46982,7 +46982,7 @@
       </c>
       <c r="AJ237" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK237" t="inlineStr">
@@ -47375,7 +47375,7 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
@@ -47768,7 +47768,7 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
@@ -48161,7 +48161,7 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
@@ -48554,7 +48554,7 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
@@ -48947,7 +48947,7 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
@@ -49340,7 +49340,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -49733,7 +49733,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -59951,7 +59951,7 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
@@ -60344,7 +60344,7 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
@@ -60737,7 +60737,7 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
@@ -61130,7 +61130,7 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
@@ -61523,7 +61523,7 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
@@ -61916,7 +61916,7 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
@@ -62309,7 +62309,7 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
@@ -62702,7 +62702,7 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
@@ -63095,7 +63095,7 @@
       </c>
       <c r="AJ319" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK319" t="inlineStr">
@@ -63488,7 +63488,7 @@
       </c>
       <c r="AJ321" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK321" t="inlineStr">
@@ -63881,7 +63881,7 @@
       </c>
       <c r="AJ323" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK323" t="inlineStr">
